--- a/data/daily/2026-10/2026-10-05.xlsx
+++ b/data/daily/2026-10/2026-10-05.xlsx
@@ -1195,14 +1195,39 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,110 +1242,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="323850" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="323850" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1450,132 +1450,132 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="866775" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="866775" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -2596,23 +2596,11 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16220</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>편리한 섭취 방식 — 액상과 정제가 일체형이라 물 없이 간편하게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>높은 선물 만족도 — 인지도 높은 명품 비타민이라 선물용으로 주고받기 좋음</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>빠른 활력 충전 — 피로 해소와 활력 증진에 즉각적인 도움을 줌</t>
-        </is>
-      </c>
+        <v>16222</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -2655,23 +2643,11 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15532</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>거부감 없는 맛 — 주스나 망고맛처럼 달콤하여 거부감 없이 맛있게 복용함</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>우수한 피로 회복 — 섭취 후 활력 증진 및 숙취 해소, 개운함을 체감함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>간편한 휴대성 — 개별 포장으로 여행이나 외출 시 챙겨 다니기 용이함</t>
-        </is>
-      </c>
+        <v>15535</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -2716,22 +2692,10 @@
       <c r="J4" t="n">
         <v>3393</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>만족스러운 피로 회복 — 힘들 때 즉각적으로 반짝하는 활력 개선 효과가 있음</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 — 패키지가 아름답고 고급스러워 선물용으로 만족도가 높음</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>발송자 확인 불편 — 보낸 사람 정보를 알기 어렵고 고객센터 응대가 미흡함</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -2773,24 +2737,12 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>6502</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 형태 — 새콤달콤한 과일 맛 젤리 형태로 간식처럼 섭취하기 좋음</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>편안한 목넘김 — 알약 대신 씹어 먹을 수 있어 삼키기 부담스러운 사람에게 적합함</t>
-        </is>
-      </c>
+        <v>6503</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>섭취량 조절의 아쉬움 — 젤리가 너무 맛있어 하루 권장량인 2개 이상 먹고 싶어짐</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -2834,26 +2786,10 @@
       <c r="J6" t="n">
         <v>8740</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>뛰어난 기력 회복 — 섭취 후 아침 피로 완화 및 기력 회복 체감이 좋음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>알찬 선물 구성 — 증정이 포함된 단독 에디션 패키지로 선물하기 적합함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>신속한 배송 — 주문 후 빠르게 받아볼 수 있어 편리함</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 포장 부피 — 소포장 위주라 겉보기에 풍성한 느낌은 덜함</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -2897,16 +2833,8 @@
       <c r="J7" t="n">
         <v>811</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>예쁜 선물용 패키지 — 박스와 종이가방 포장이 고급스러워 명절 선물로 만족스러움</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>환절기 활력 증진 — 면역력 유지 및 즉각적인 피로 해소에 도움을 줌</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -2950,23 +2878,11 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>809</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>간편한 휴대 복용 — 마시는 형태의 올인원 비타민으로 휴대가 편하고 복용이 쉬움</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>빠른 배송 및 가성비 — 배송이 신속하며 합리적인 가격대에 구매 가능함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>일상 활력 증진 — 직장 업무나 아침 피로 회복에 에너지를 보충해줌</t>
-        </is>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -3011,26 +2927,10 @@
       <c r="J9" t="n">
         <v>779</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>성별 맞춤 선택 — 남성과 여성에 맞는 성분 조합으로 골라 마실 수 있음</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>부담 없는 풍미 — 비타민 특유의 쓴맛이 없어 편안하게 복용 가능함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>긴 활력 유지감 — 섭취 후 활력이 오래 지속되는 만족감을 줌</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>알약 크기 부담 — 정제 크기가 다소 커서 한 번에 삼키기 부담스러움</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -3072,28 +2972,12 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>1734</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>아이디어 용기 설계 — 분말과 액상이 분리 보관되어 버튼을 눌러 섞어 마시는 재미가 있음</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>달콤하고 상큼한 맛 — 쓴맛 없이 달달하여 어린이나 어르신 모두 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 — 전용 봉투와 패키지가 잘 갖춰져 선물용으로 훌륭함</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>뚜껑 개봉의 어려움 — 용기 구조상 손 힘이 약한 사람은 뚜껑을 열기 다소 힘듦</t>
-        </is>
-      </c>
+        <v>1735</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -3135,29 +3019,13 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>945</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>신뢰받는 원료 — 영국산 비타민C 원료를 사용하여 꾸준히 믿고 섭취함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>확실한 정신 환기 — 고함량 비타민C 복용으로 기운 충전 및 개운함을 느낌</t>
-        </is>
-      </c>
+        <v>946</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>강한 신맛과 불호 — 가루 형태의 신맛이 매우 강해 섭취가 부담스럽고 맛이 없음</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>제형의 아쉬움 — 분말 대신 캡슐 형태로 제공되었으면 하는 바람이 있음</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
     <row r="12" ht="38" customHeight="1">
@@ -3198,23 +3066,11 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>156</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>만족스러운 맛 — 소다맛 뽕따향이 나며 달달하고 텁텁하지 않음</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>콜라보 굿즈 구성 — 리센느 포토카드 및 사은품 구성으로 팬 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>입자감 및 편의성 — 분말 입자가 곱고 식후 간편하게 섭취하기 좋음</t>
-        </is>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -3259,26 +3115,10 @@
       <c r="J13" t="n">
         <v>60</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>부드럽고 촉촉한 육질 — 닭가슴살 특유의 퍽퍽함 없이 부드럽고 냄새가 나지 않음</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>다양한 맛과 구성 — 소스 통살, 스테이크 등 종류가 다양해 질리지 않고 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>훌륭한 가성비 — 할인 행사가 자주 진행되어 저렴한 가격에 구매 가능함</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>선호 품목 제외 아쉬움 — 구성 내 파우치형 그릴 제품이 빠져 있어 아쉬움이 있음</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -3322,33 +3162,17 @@
       <c r="J14" t="n">
         <v>1687</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>속 편한 소화감 — 밀가루 섭취 후 복용 시 더부룩하지 않고 속이 편안함</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>구수한 고구마 맛 — 거부감 없는 구수한 고구마 풍미로 온 가족이 즐기기 좋음</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>풍성한 사은품 구성 — 파로 곡물바 및 추가 효소 증정으로 세트 구성이 알참</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>가격 할인 요청 — 꾸준히 먹기 위해 세일 행사가 더 잦았으면 함</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3356,62 +3180,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>86,800원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>152</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>든든한 포만감과 맛 — 맛이 좋아 물리지 않으며 한 개만 먹어도 식사 대용으로 든든함</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>사은품 보냉백 증정 — 도시락 가방으로 쓰기 좋은 사은품이 동봉되어 유용함</t>
-        </is>
-      </c>
+        <v>754</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>오배송 및 문의 응대 미흡 — 구성품이 중복 배송되었으나 문의 답변이 지연됨</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>포장 불량 및 터짐 — 진공포장이 헐겁거나 팩이 터져 소스가 새어 나옴</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3419,51 +3227,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>86,800원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>753</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>고급스러운 오간자 패키지 — 플리츠백과 고급 포장이 함께 제공되어 선물 감동이 큼</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>맛있고 간편한 복용 — 액상 앰플 형태로 맛이 좋아 매일 챙겨 마시기 편함</t>
-        </is>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 가격대가 있어 할인 행사 없이 구매하기엔 다소 부담스러움</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
@@ -3507,26 +3303,10 @@
       <c r="J17" t="n">
         <v>69</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>촉촉하고 쫄깃한 식감 — 퍽퍽하지 않고 부드러우며 간이 알맞아 맛있음</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>간편한 조리 편의성 — 전자레인지로 쉽게 데워 먹을 수 있어 식단 관리에 용이함</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>골라 먹는 구성 — 소스통살과 볼 형태가 섞여 있어 샐러드 곁들임에 좋음</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>다소 늦은 배송 — 일부 배송 과정이 다소 지연되어 늦게 도착함</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3570,16 +3350,8 @@
       <c r="J18" t="n">
         <v>217</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>텁텁함 없는 맛 — 프로틴 특유의 비린 맛 없이 진하고 달콤한 음료 느낌임</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>운동 후 단백질 보충 — 운동 후 허기짐을 달래고 단백질을 챙기기에 적합함</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -3625,21 +3397,9 @@
       <c r="J19" t="n">
         <v>248</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>고함량 빠른 활력 체감 — 6200mg 고함량으로 운동 시 지구력 및 일상 피로 개선에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>선물용 패키지 구성 — 쇼핑백과 추가 증정분이 동봉되어 선물용으로 훌륭함</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>간편한 섭취 편의성 — 하루 한 포 개별 포장으로 휴대가 편하고 복용이 쉬움</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3684,21 +3444,9 @@
       <c r="J20" t="n">
         <v>903</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>편안한 소화감 — 꾸준히 섭취 시 배변 활동과 소화에 긍정적인 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>알찬 가격과 사은품 — 저렴한 구성에 저당씬칩 등 간식이 함께 제공되어 만족스러움</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>부담 없는 맛 — 거부감 없는 맛으로 남녀노소 즐기기 편함</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3743,26 +3491,10 @@
       <c r="J21" t="n">
         <v>21</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>확실한 숙취 해소 체감 — 음주 전후 섭취 시 다음 날 아침 두통과 피로감이 덜함</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>간편한 스틱 액상 — 물 없이 간편하게 뜯어 마실 수 있어 술자리 휴대가 편리함</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>고급스러운 선물 패키지 — 전용 쇼핑백과 보라색 패키지가 정갈하여 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>한약재 풍미 호불호 — 쌍화탕이나 한약 느낌의 쓴맛이 있어 개인 취향을 탈 수 있음</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -4084,16 +3816,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16220</v>
+        <v>16222</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15532</v>
+        <v>15535</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3393</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6502</v>
+        <v>6503</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>8740</v>
@@ -4102,92 +3834,36 @@
         <v>811</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>779</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>편리한 섭취 방식 — 액상과 정제가 일체형이라 물 없이 간편하게 섭취 가능함
-높은 선물 만족도 — 인지도 높은 명품 비타민이라 선물용으로 주고받기 좋음
-빠른 활력 충전 — 피로 해소와 활력 증진에 즉각적인 도움을 줌</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>거부감 없는 맛 — 주스나 망고맛처럼 달콤하여 거부감 없이 맛있게 복용함
-우수한 피로 회복 — 섭취 후 활력 증진 및 숙취 해소, 개운함을 체감함
-간편한 휴대성 — 개별 포장으로 여행이나 외출 시 챙겨 다니기 용이함</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>만족스러운 피로 회복 — 힘들 때 즉각적으로 반짝하는 활력 개선 효과가 있음
-고급스러운 포장 — 패키지가 아름답고 고급스러워 선물용으로 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 형태 — 새콤달콤한 과일 맛 젤리 형태로 간식처럼 섭취하기 좋음
-편안한 목넘김 — 알약 대신 씹어 먹을 수 있어 삼키기 부담스러운 사람에게 적합함</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>뛰어난 기력 회복 — 섭취 후 아침 피로 완화 및 기력 회복 체감이 좋음
-알찬 선물 구성 — 증정이 포함된 단독 에디션 패키지로 선물하기 적합함
-신속한 배송 — 주문 후 빠르게 받아볼 수 있어 편리함</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>예쁜 선물용 패키지 — 박스와 종이가방 포장이 고급스러워 명절 선물로 만족스러움
-환절기 활력 증진 — 면역력 유지 및 즉각적인 피로 해소에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>간편한 휴대 복용 — 마시는 형태의 올인원 비타민으로 휴대가 편하고 복용이 쉬움
-빠른 배송 및 가성비 — 배송이 신속하며 합리적인 가격대에 구매 가능함
-일상 활력 증진 — 직장 업무나 아침 피로 회복에 에너지를 보충해줌</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>성별 맞춤 선택 — 남성과 여성에 맞는 성분 조합으로 골라 마실 수 있음
-부담 없는 풍미 — 비타민 특유의 쓴맛이 없어 편안하게 복용 가능함
-긴 활력 유지감 — 섭취 후 활력이 오래 지속되는 만족감을 줌</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>아이디어 용기 설계 — 분말과 액상이 분리 보관되어 버튼을 눌러 섞어 마시는 재미가 있음
-달콤하고 상큼한 맛 — 쓴맛 없이 달달하여 어린이나 어르신 모두 먹기 편함
-고급스러운 포장 — 전용 봉투와 패키지가 잘 갖춰져 선물용으로 훌륭함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>신뢰받는 원료 — 영국산 비타민C 원료를 사용하여 꾸준히 믿고 섭취함
-확실한 정신 환기 — 고함량 비타민C 복용으로 기운 충전 및 개운함을 느낌</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4195,39 +3871,14 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>발송자 확인 불편 — 보낸 사람 정보를 알기 어렵고 고객센터 응대가 미흡함</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>섭취량 조절의 아쉬움 — 젤리가 너무 맛있어 하루 권장량인 2개 이상 먹고 싶어짐</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 포장 부피 — 소포장 위주라 겉보기에 풍성한 느낌은 덜함</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>알약 크기 부담 — 정제 크기가 다소 커서 한 번에 삼키기 부담스러움</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>뚜껑 개봉의 어려움 — 용기 구조상 손 힘이 약한 사람은 뚜껑을 열기 다소 힘듦</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>강한 신맛과 불호 — 가루 형태의 신맛이 매우 강해 섭취가 부담스럽고 맛이 없음
-제형의 아쉬움 — 분말 대신 캡슐 형태로 제공되었으면 하는 바람이 있음</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4440,12 +4091,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4497,12 +4148,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -4554,12 +4205,12 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -4632,7 +4283,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>60</v>
@@ -4641,10 +4292,10 @@
         <v>1687</v>
       </c>
       <c r="F19" s="3" t="n">
+        <v>754</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>152</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>753</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>69</v>
@@ -4662,121 +4313,39 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" ht="90" customHeight="1">
+    <row r="20">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>만족스러운 맛 — 소다맛 뽕따향이 나며 달달하고 텁텁하지 않음
-콜라보 굿즈 구성 — 리센느 포토카드 및 사은품 구성으로 팬 만족도가 높음
-입자감 및 편의성 — 분말 입자가 곱고 식후 간편하게 섭취하기 좋음</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>부드럽고 촉촉한 육질 — 닭가슴살 특유의 퍽퍽함 없이 부드럽고 냄새가 나지 않음
-다양한 맛과 구성 — 소스 통살, 스테이크 등 종류가 다양해 질리지 않고 섭취 가능함
-훌륭한 가성비 — 할인 행사가 자주 진행되어 저렴한 가격에 구매 가능함</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>속 편한 소화감 — 밀가루 섭취 후 복용 시 더부룩하지 않고 속이 편안함
-구수한 고구마 맛 — 거부감 없는 구수한 고구마 풍미로 온 가족이 즐기기 좋음
-풍성한 사은품 구성 — 파로 곡물바 및 추가 효소 증정으로 세트 구성이 알참</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>든든한 포만감과 맛 — 맛이 좋아 물리지 않으며 한 개만 먹어도 식사 대용으로 든든함
-사은품 보냉백 증정 — 도시락 가방으로 쓰기 좋은 사은품이 동봉되어 유용함</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>고급스러운 오간자 패키지 — 플리츠백과 고급 포장이 함께 제공되어 선물 감동이 큼
-맛있고 간편한 복용 — 액상 앰플 형태로 맛이 좋아 매일 챙겨 마시기 편함</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>촉촉하고 쫄깃한 식감 — 퍽퍽하지 않고 부드러우며 간이 알맞아 맛있음
-간편한 조리 편의성 — 전자레인지로 쉽게 데워 먹을 수 있어 식단 관리에 용이함
-골라 먹는 구성 — 소스통살과 볼 형태가 섞여 있어 샐러드 곁들임에 좋음</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>텁텁함 없는 맛 — 프로틴 특유의 비린 맛 없이 진하고 달콤한 음료 느낌임
-운동 후 단백질 보충 — 운동 후 허기짐을 달래고 단백질을 챙기기에 적합함</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>고함량 빠른 활력 체감 — 6200mg 고함량으로 운동 시 지구력 및 일상 피로 개선에 도움을 줌
-선물용 패키지 구성 — 쇼핑백과 추가 증정분이 동봉되어 선물용으로 훌륭함
-간편한 섭취 편의성 — 하루 한 포 개별 포장으로 휴대가 편하고 복용이 쉬움</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>편안한 소화감 — 꾸준히 섭취 시 배변 활동과 소화에 긍정적인 도움을 줌
-알찬 가격과 사은품 — 저렴한 구성에 저당씬칩 등 간식이 함께 제공되어 만족스러움
-부담 없는 맛 — 거부감 없는 맛으로 남녀노소 즐기기 편함</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>확실한 숙취 해소 체감 — 음주 전후 섭취 시 다음 날 아침 두통과 피로감이 덜함
-간편한 스틱 액상 — 물 없이 간편하게 뜯어 마실 수 있어 술자리 휴대가 편리함
-고급스러운 선물 패키지 — 전용 쇼핑백과 보라색 패키지가 정갈하여 선물용으로 적합함</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>선호 품목 제외 아쉬움 — 구성 내 파우치형 그릴 제품이 빠져 있어 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>가격 할인 요청 — 꾸준히 먹기 위해 세일 행사가 더 잦았으면 함</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>오배송 및 문의 응대 미흡 — 구성품이 중복 배송되었으나 문의 답변이 지연됨
-포장 불량 및 터짐 — 진공포장이 헐겁거나 팩이 터져 소스가 새어 나옴</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 가격대가 있어 할인 행사 없이 구매하기엔 다소 부담스러움</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>다소 늦은 배송 — 일부 배송 과정이 다소 지연되어 늦게 도착함</t>
-        </is>
-      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>한약재 풍미 호불호 — 쌍화탕이나 한약 느낌의 쓴맛이 있어 개인 취향을 탈 수 있음</t>
-        </is>
-      </c>
+      <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4801,12 +4370,12 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
+          <t>65,900원</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
           <t>86,800원</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>65,900원</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5029,51 +4598,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>종근당 데일리와이즈 테아닌 구미 7일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306209&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260417/rS9JgHwoY8ffaFGoRZTx032306209_00_01rS9JgHwoY8ffaFGoRZTx.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>516</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>시원한 배변 활동 — 복용 후 변이 묽어지며 장 비우기에 확실한 체감을 줌</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 부담 없는 가격에 구매하여 비상용으로 마시기 좋음</t>
-        </is>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>체감 효과의 개인차 — 심한 변비의 경우 편의점 제품 대비 강도가 약하게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -5088,45 +4645,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306208&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260417/wEewWmXsoUl4j1ERyFu9032306208_00_01wEewWmXsoUl4j1ERyFu9.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1231</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>합리적인 가격대 — 한 달분 기준으로 가성비가 뛰어나 정기 구매하기 좋음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>신뢰할 수 있는 소연골 베이스 — 대웅제약 제조 및 소연골 원료로 부모님 선물용으로 믿음직함</t>
-        </is>
-      </c>
+        <v>668</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -5135,7 +4684,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5143,7 +4692,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 츄어블 60정 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5153,52 +4702,36 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000142&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/CJUce0AJqtqHn7R3ZFm1600000142_00_00CJUce0AJqtqHn7R3ZFm1.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>621</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>씹어 먹는 츄어블 제형 — 알약을 삼키기 힘든 성인이나 아이가 사탕처럼 쉽게 섭취함</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>맛있는 복용감 — 영양제 특유의 거부감 없이 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
+        <v>6595</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>잦은 품절 현상 — 인기 상품이라 재고가 부족해 미리 쟁여두어야 함</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>치아 끼임 및 쇠맛 — 씹을 때 치아에 끼면 철분 맛이 느껴질 수 있어 양치가 필요함</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5206,7 +4739,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[의약외품][신혜선 PICK] 동국제약 멜라케어 더블 화이트 정 10정 10일분</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5216,48 +4749,36 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911058&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260710/ttaHg18AMnzwMvyaF63v610911058_00_00ttaHg18AMnzwMvyaF63v.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>171</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>제약사 신뢰도 — 동국제약 의약외품이라 성분에 대한 믿음을 가짐</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>간편한 접근성 — 다이소 매장에서 손쉽게 소용량으로 시도해볼 수 있음</t>
-        </is>
-      </c>
+        <v>2867</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>미미한 미백 체감 — 20일 이상 섭취해도 눈에 띄는 피부 톤 개선 효과를 느끼기 어려움</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5265,12 +4786,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
+          <t>동국제약 혈당케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5280,30 +4801,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250430/yuK2zGjcuX8RmMDP9k9P591580541_00_00yuK2zGjcuX8RmMDP9k9P.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/y6DqUAmlgLsAXGUrvbmN610910678_00_00y6DqUAmlgLsAXGUrvbmN.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1777</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>부담 없는 초가성비 — 저렴한 가격으로 매달 부담 없이 눈 건강을 챙길 수 있음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>복합 영양 설계 — 루테인지아잔틴 외에 비타민 성분이 함께 들어 있어 만족스러움</t>
-        </is>
-      </c>
+        <v>1591</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -5312,7 +4825,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5320,51 +4833,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
+          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953528&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/9Cz26kBHEVc4QcQuToeY994953528_00_009Cz26kBHEVc4QcQuToeY.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260409/2cHZmOZUJJcZL1ip2bls610910968_00_002cHZmOZUJJcZL1ip2bls.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.7</v>
       </c>
       <c r="J7" t="n">
-        <v>543</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>부담 없는 시도 가격 — 저렴한 가격으로 콜라겐 스틱을 부담 없이 맛볼 수 있음</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>맛있는 간식 느낌 — 맛이 좋아 가볍게 섭취하기에 용이함</t>
-        </is>
-      </c>
+        <v>2518</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>적은 용량 대비 아쉬움 — 7포 소용량이라 단기간 섭취로 피부 변화를 체감하긴 어려움</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -5379,51 +4880,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>자연관 정성담은 배도라지스틱 12포</t>
+          <t>[의약외품] 동화 퀵앤써액 복숭아 12ml 5포</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762093&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618634&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260508/SdledEzpIdjdFFQW6W8g901762093_00_00SdledEzpIdjdFFQW6W8g.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260424/G3OpB4vFrKk7H6gBBjO3601618634_00_00G3OpB4vFrKk7H6gBBjO3.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>927</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>목 완화에 좋은 단맛 — 달콤한 원액이라 아이들도 잘 먹고 환절기 목 보호에 좋음</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>휴대용 스틱 포장 — 개별 포장으로 외출 시 하나씩 들고 다니며 짜 먹기 편함</t>
-        </is>
-      </c>
+        <v>821</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>과도한 당도 — 단맛이 다소 강해 공복 섭취가 부담스럽고 물에 타면 밍밍함</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -5438,45 +4927,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1643</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 유기농 레몬즙을 저렴한 가격에 부담 없이 구매 가능함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>간편한 개별 포장 — 한 포씩 소포장되어 계량 없이 레몬에이드나 요리에 바로 사용함</t>
-        </is>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -5493,12 +4974,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>동국제약 마데카 저분자 콜라겐C</t>
+          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5508,43 +4989,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910603&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953529&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250530/iFPtDwREEwh2EwWoojJJ610910603_00_01iFPtDwREEwh2EwWoojJJ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/vXg1N5D0xbSNweDPvvl2994953529_00_00vXg1N5D0xbSNweDPvvl2.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>705</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>비리지 않은 목넘김 — 달콤하고 느끼함이 없어 목으로 부드럽게 잘 넘어감</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>합리적인 가격대 — 저렴한 가격으로 저분자 콜라겐을 챙겨 먹기 적합함</t>
-        </is>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>체감 효과의 모호함 — 피부 개선 체감이 미미하거나 단기간에는 알기 어려움</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5552,56 +5021,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 히알루론산 더마스틱 12포</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953531&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/9sKzBlRNgLc6DDH1QsJU994953531_00_009sKzBlRNgLc6DDH1QsJU.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>499</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>상큼한 파인애플맛 — 파인애플 맛으로 물에 타서 음료 대용으로 마시기 수월함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>대기업 브랜드 신뢰 — LG생활건강 브랜드 제품이라 믿고 섭취함</t>
-        </is>
-      </c>
+        <v>2762</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>짧은 유통기한 — 수령 후 소비기한이 다음 달까지로 다소 임박하게 배송됨</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>짧은 기간 내 미미한 효과 — 12포 분량으로는 피부 보습 효과를 체감하기에 다소 부족함</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5725,42 +5178,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -5772,52 +5225,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>종근당</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>종근당</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>이너뷰 바이 리튠</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>홀베리</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>셀트리온</t>
         </is>
       </c>
     </row>
@@ -5829,52 +5282,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>종근당 데일리와이즈 테아닌 구미 7일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[의약외품] 동화 퀵앤써액 복숭아 12ml 5포</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 멀티비타민 미네랄 츄어블 60정 30일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[의약외품][신혜선 PICK] 동국제약 멜라케어 더블 화이트 정 10정 10일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>자연관 정성담은 배도라지스틱 12포</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 마데카 저분자 콜라겐C</t>
+          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 히알루론산 더마스틱 12포</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
     </row>
@@ -5885,16 +5338,16 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
@@ -5903,16 +5356,16 @@
         <v>4.7</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -5922,149 +5375,69 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
+        <v>386</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>668</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>6595</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2867</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1591</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>2518</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>821</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>516</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>1231</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>621</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1777</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>543</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>927</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>1643</v>
-      </c>
       <c r="K7" s="3" t="n">
-        <v>705</v>
+        <v>395</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>시원한 배변 활동 — 복용 후 변이 묽어지며 장 비우기에 확실한 체감을 줌
-뛰어난 가성비 — 부담 없는 가격에 구매하여 비상용으로 마시기 좋음</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>합리적인 가격대 — 한 달분 기준으로 가성비가 뛰어나 정기 구매하기 좋음
-신뢰할 수 있는 소연골 베이스 — 대웅제약 제조 및 소연골 원료로 부모님 선물용으로 믿음직함</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>씹어 먹는 츄어블 제형 — 알약을 삼키기 힘든 성인이나 아이가 사탕처럼 쉽게 섭취함
-맛있는 복용감 — 영양제 특유의 거부감 없이 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>제약사 신뢰도 — 동국제약 의약외품이라 성분에 대한 믿음을 가짐
-간편한 접근성 — 다이소 매장에서 손쉽게 소용량으로 시도해볼 수 있음</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>부담 없는 초가성비 — 저렴한 가격으로 매달 부담 없이 눈 건강을 챙길 수 있음
-복합 영양 설계 — 루테인지아잔틴 외에 비타민 성분이 함께 들어 있어 만족스러움</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>부담 없는 시도 가격 — 저렴한 가격으로 콜라겐 스틱을 부담 없이 맛볼 수 있음
-맛있는 간식 느낌 — 맛이 좋아 가볍게 섭취하기에 용이함</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>목 완화에 좋은 단맛 — 달콤한 원액이라 아이들도 잘 먹고 환절기 목 보호에 좋음
-휴대용 스틱 포장 — 개별 포장으로 외출 시 하나씩 들고 다니며 짜 먹기 편함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 유기농 레몬즙을 저렴한 가격에 부담 없이 구매 가능함
-간편한 개별 포장 — 한 포씩 소포장되어 계량 없이 레몬에이드나 요리에 바로 사용함</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>비리지 않은 목넘김 — 달콤하고 느끼함이 없어 목으로 부드럽게 잘 넘어감
-합리적인 가격대 — 저렴한 가격으로 저분자 콜라겐을 챙겨 먹기 적합함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>상큼한 파인애플맛 — 파인애플 맛으로 물에 타서 음료 대용으로 마시기 수월함
-대기업 브랜드 신뢰 — LG생활건강 브랜드 제품이라 믿고 섭취함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>체감 효과의 개인차 — 심한 변비의 경우 편의점 제품 대비 강도가 약하게 느껴짐</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>잦은 품절 현상 — 인기 상품이라 재고가 부족해 미리 쟁여두어야 함
-치아 끼임 및 쇠맛 — 씹을 때 치아에 끼면 철분 맛이 느껴질 수 있어 양치가 필요함</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>미미한 미백 체감 — 20일 이상 섭취해도 눈에 띄는 피부 톤 개선 효과를 느끼기 어려움</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>적은 용량 대비 아쉬움 — 7포 소용량이라 단기간 섭취로 피부 변화를 체감하긴 어려움</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>과도한 당도 — 단맛이 다소 강해 공복 섭취가 부담스럽고 물에 타면 밍밍함</t>
-        </is>
-      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>체감 효과의 모호함 — 피부 개선 체감이 미미하거나 단기간에는 알기 어려움</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>짧은 유통기한 — 수령 후 소비기한이 다음 달까지로 다소 임박하게 배송됨
-짧은 기간 내 미미한 효과 — 12포 분량으로는 피부 보습 효과를 체감하기에 다소 부족함</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6074,52 +5447,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>2,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
     </row>
@@ -6372,27 +5745,11 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>557</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>이중 기능성 설계 — 체지방 감소와 장 건강 케어를 동시에 할 수 있어 만족스러움</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>상큼한 요거트맛 — 맛있는 요거트 맛 분말이라 매일 거부감 없이 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>편안한 속과 붓기 완화 — 복용 후 더부룩함이 줄어들고 아랫배 관리에 도움을 줌</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -6400,7 +5757,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6408,35 +5765,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>269</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -6447,7 +5800,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6455,58 +5808,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>26981</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>확실한 단기 감량 체감 — 과식 후 붓기 제거 및 뱃살 정리에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>배변 활동 원활 — 클렌즈 섭취 후 화장실을 수월하게 갈 수 있음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 정제 크기가 다소 커서 삼킬 때 부담스러울 수 있음</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6514,40 +5851,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246271&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627107ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>154</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>달콤한 복숭아맛 — 초딩 입맛도 거부감 없이 맛있게 섭취할 수 있는 복숭아 맛임</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -6557,7 +5886,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6565,31 +5894,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[1+1]알디콤 Plus 숙취해소제 21ml 4포입</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>17,300원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227457&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022745735ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3650</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -6600,7 +5933,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6608,35 +5941,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[올영단독] 세렌 리스펙타 질 유산균 플러스 15캡슐 (15일분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>세렌</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27,000원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263046&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026304608ko.png?l=ko</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587421ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -6655,50 +5984,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>17161</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>즉각적인 붓기 완화 — 야식이나 짠 음식 섭취 후 얼굴 붓기 및 윤곽 정리에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>삼키기 편한 미니환 — 알약 크기가 작은 미니환 형태라 목넘김이 수월함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>간편한 휴대 복용 — 개별 스틱으로 파우치에 넣어 다니며 중요한 일정 전에 먹기 좋음</t>
-        </is>
-      </c>
+        <v>15941</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -6706,7 +6023,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6714,50 +6031,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59,000원</t>
+          <t>24,500원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>412</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>질과 장 동시 케어 — 여성 질 건강과 장 건강을 한 번에 챙길 수 있는 더블 기능성임</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>작은 캡슐 크기 — 캡슐 크기가 작아 목 넘김이 매우 수월하고 복용이 편함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>귀여운 콜라보 굿즈 — 포켓몬 에디션 카드케이스 등 기획 상품의 실용성과 만족도가 높음</t>
-        </is>
-      </c>
+        <v>19300</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -6765,7 +6070,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6773,50 +6078,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>아이힐 비너스 질유산균 30캡슐 (+6캡슐) 증량 기획</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>아이힐</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28,400원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000217101&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021710167ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4465</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>크랜베리 복합 성분 — 질 유래 유산균 외에 여성에게 유익한 크랜베리 성분이 함유됨</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>여성 컨디션 밸런스 개선 — 꾸준히 복용 시 여성 질환 예방 및 생리 불균형 관리에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>추가 증량 기획 — 본품에 6캡슐이 추가 증정되어 실속 있는 구성임</t>
-        </is>
-      </c>
+        <v>19703</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -6942,27 +6235,27 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -6972,12 +6265,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -6999,42 +6292,42 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>세렌</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>아이힐</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
     </row>
@@ -7056,42 +6349,42 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[1+1]알디콤 Plus 숙취해소제 21ml 4포입</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[올영단독] 세렌 리스펙타 질 유산균 플러스 15캡슐 (15일분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>아이힐 비너스 질유산균 30캡슐 (+6캡슐) 증량 기획</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
     </row>
@@ -7102,30 +6395,22 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E6" s="3" t="n">
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -7135,81 +6420,40 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="n">
-        <v>557</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>269</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>26981</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n">
+        <v>3650</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>17161</v>
+        <v>15941</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>412</v>
+        <v>19300</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>4465</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>19703</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>이중 기능성 설계 — 체지방 감소와 장 건강 케어를 동시에 할 수 있어 만족스러움
-상큼한 요거트맛 — 맛있는 요거트 맛 분말이라 매일 거부감 없이 섭취 가능함
-편안한 속과 붓기 완화 — 복용 후 더부룩함이 줄어들고 아랫배 관리에 도움을 줌</t>
-        </is>
-      </c>
+      <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>확실한 단기 감량 체감 — 과식 후 붓기 제거 및 뱃살 정리에 도움을 줌
-배변 활동 원활 — 클렌즈 섭취 후 화장실을 수월하게 갈 수 있음</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>달콤한 복숭아맛 — 초딩 입맛도 거부감 없이 맛있게 섭취할 수 있는 복숭아 맛임</t>
-        </is>
-      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>즉각적인 붓기 완화 — 야식이나 짠 음식 섭취 후 얼굴 붓기 및 윤곽 정리에 도움을 줌
-삼키기 편한 미니환 — 알약 크기가 작은 미니환 형태라 목넘김이 수월함
-간편한 휴대 복용 — 개별 스틱으로 파우치에 넣어 다니며 중요한 일정 전에 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>질과 장 동시 케어 — 여성 질 건강과 장 건강을 한 번에 챙길 수 있는 더블 기능성임
-작은 캡슐 크기 — 캡슐 크기가 작아 목 넘김이 매우 수월하고 복용이 편함
-귀여운 콜라보 굿즈 — 포켓몬 에디션 카드케이스 등 기획 상품의 실용성과 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>크랜베리 복합 성분 — 질 유래 유산균 외에 여성에게 유익한 크랜베리 성분이 함유됨
-여성 컨디션 밸런스 개선 — 꾸준히 복용 시 여성 질환 예방 및 생리 불균형 관리에 도움을 줌
-추가 증량 기획 — 본품에 6캡슐이 추가 증정되어 실속 있는 구성임</t>
-        </is>
-      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7220,11 +6464,7 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 정제 크기가 다소 커서 삼킬 때 부담스러울 수 있음</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
@@ -7250,42 +6490,42 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>17,300원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>27,000원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>59,000원</t>
+          <t>24,500원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>28,400원</t>
+          <t>5,900원</t>
         </is>
       </c>
     </row>
@@ -7415,10 +6655,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -7427,70 +6667,70 @@
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -7499,23 +6739,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
-        <v>12.5</v>
-      </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -7543,7 +6783,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7553,10 +6793,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7565,7 +6805,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7575,10 +6815,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
